--- a/assets/files/coca-cola-business-model.xlsx
+++ b/assets/files/coca-cola-business-model.xlsx
@@ -8,13 +8,16 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Ratios" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer Comps" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Ratios" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer Comps" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Valuation Summary'!$A$1:$E$29</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -31,7 +34,7 @@
     <numFmt numFmtId="170" formatCode="0.0&quot;x&quot;"/>
     <numFmt numFmtId="171" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -193,8 +196,13 @@
       <color rgb="00595959"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -239,6 +247,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF2F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E5496"/>
       </patternFill>
     </fill>
   </fills>
@@ -437,7 +455,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -817,6 +835,13 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1327,6 +1352,349 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" style="59" min="1" max="1"/>
+    <col width="24" customWidth="1" style="59" min="2" max="2"/>
+    <col width="14" customWidth="1" style="59" min="3" max="3"/>
+    <col width="14" customWidth="1" style="59" min="4" max="4"/>
+    <col width="14" customWidth="1" style="59" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="139" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company (KO) — Multi-Method Valuation Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="58" t="inlineStr">
+        <is>
+          <t>USD; per-share USD. Dividend aristocrat (63+ yrs) — DDM-led. Live $82 (Jul 2026), 4,310M shares, net debt ~$29bn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="140" t="inlineStr">
+        <is>
+          <t>KEY INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="58" t="inlineStr">
+        <is>
+          <t>Live share price ($)</t>
+        </is>
+      </c>
+      <c r="B5" s="141" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="58" t="inlineStr">
+        <is>
+          <t>Shares (M)</t>
+        </is>
+      </c>
+      <c r="B6" s="141" t="n">
+        <v>4310</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="58" t="inlineStr">
+        <is>
+          <t>Net debt ($M)</t>
+        </is>
+      </c>
+      <c r="B7" s="141" t="n">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="58" t="inlineStr">
+        <is>
+          <t>FY25 comparable EPS ($)</t>
+        </is>
+      </c>
+      <c r="B8" s="58" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="58" t="inlineStr">
+        <is>
+          <t>FY26E EPS ($)</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="58" t="inlineStr">
+        <is>
+          <t>FY25 dividend/share ($)</t>
+        </is>
+      </c>
+      <c r="B10" s="58" t="n">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="58" t="inlineStr">
+        <is>
+          <t>FY26E EBITDA ($M)</t>
+        </is>
+      </c>
+      <c r="B11" s="141" t="n">
+        <v>15100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="58" t="inlineStr">
+        <is>
+          <t>Normalized FCF ($M)</t>
+        </is>
+      </c>
+      <c r="B12" s="141" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="58" t="inlineStr">
+        <is>
+          <t>Cost of equity Ke</t>
+        </is>
+      </c>
+      <c r="B13" s="58" t="n">
+        <v>0.0725</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="58" t="inlineStr">
+        <is>
+          <t>Dividend growth g (Gordon)</t>
+        </is>
+      </c>
+      <c r="B14" s="58" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="140" t="inlineStr">
+        <is>
+          <t>VALUATION METHODS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="142" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B17" s="142" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="C17" s="142" t="inlineStr">
+        <is>
+          <t>Value/share ($)</t>
+        </is>
+      </c>
+      <c r="D17" s="142" t="inlineStr">
+        <is>
+          <t>vs price</t>
+        </is>
+      </c>
+      <c r="E17" s="142" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="58" t="inlineStr">
+        <is>
+          <t>Dividend discount (Gordon)</t>
+        </is>
+      </c>
+      <c r="B18" s="58" t="inlineStr">
+        <is>
+          <t>Ke 7.25%, g 5%</t>
+        </is>
+      </c>
+      <c r="C18" s="143">
+        <f>B10*(1+B14)/(B13-B14)</f>
+        <v/>
+      </c>
+      <c r="D18" s="144">
+        <f>C18/B5-1</f>
+        <v/>
+      </c>
+      <c r="E18" s="145" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="58" t="inlineStr">
+        <is>
+          <t>P/E (relative)</t>
+        </is>
+      </c>
+      <c r="B19" s="58" t="inlineStr">
+        <is>
+          <t>27x × FY26E EPS</t>
+        </is>
+      </c>
+      <c r="C19" s="143">
+        <f>27*B9</f>
+        <v/>
+      </c>
+      <c r="D19" s="144">
+        <f>C19/B5-1</f>
+        <v/>
+      </c>
+      <c r="E19" s="145" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="58" t="inlineStr">
+        <is>
+          <t>EV/EBITDA (relative)</t>
+        </is>
+      </c>
+      <c r="B20" s="58" t="inlineStr">
+        <is>
+          <t>24x × FY26E EBITDA</t>
+        </is>
+      </c>
+      <c r="C20" s="143">
+        <f>(24*B11-B7)/B6</f>
+        <v/>
+      </c>
+      <c r="D20" s="144">
+        <f>C20/B5-1</f>
+        <v/>
+      </c>
+      <c r="E20" s="145" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="58" t="inlineStr">
+        <is>
+          <t>DCF (conservative floor)</t>
+        </is>
+      </c>
+      <c r="B21" s="58" t="inlineStr">
+        <is>
+          <t>FCF, WACC 7%, term g 3%</t>
+        </is>
+      </c>
+      <c r="C21" s="143" t="n">
+        <v>59</v>
+      </c>
+      <c r="D21" s="144">
+        <f>C21/B5-1</f>
+        <v/>
+      </c>
+      <c r="E21" s="145" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="140" t="inlineStr">
+        <is>
+          <t>BLENDED VALUATION &amp; RATING</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="58" t="inlineStr">
+        <is>
+          <t>Blended fair value ($)</t>
+        </is>
+      </c>
+      <c r="B24" s="143">
+        <f>SUMPRODUCT(C18:C21,E18:E21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="58" t="inlineStr">
+        <is>
+          <t>Upside / (downside) vs $82</t>
+        </is>
+      </c>
+      <c r="B25" s="144">
+        <f>B24/B5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="58" t="inlineStr">
+        <is>
+          <t>Rating (total-return basis)</t>
+        </is>
+      </c>
+      <c r="B26" s="58">
+        <f>IF(B29&gt;0.14,"BUY",IF(B29&gt;0.06,"ACCUMULATE",IF(B29&gt;-0.04,"HOLD","REDUCE")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="58" t="inlineStr">
+        <is>
+          <t>Note: A dividend aristocrat is best valued DDM-first; relative multiples (P/E, EV/EBITDA) capture the durable staple premium; the DCF is a conservative floor. ~2.6% growing yield adds to the total-return case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="58" t="inlineStr">
+        <is>
+          <t>Dividend yield (D/P)</t>
+        </is>
+      </c>
+      <c r="B28" s="144">
+        <f>B10/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="58" t="inlineStr">
+        <is>
+          <t>Total expected return (price + yield)</t>
+        </is>
+      </c>
+      <c r="B29" s="144">
+        <f>B25+B28</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A23:E23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FFB00D18"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2294,7 +2662,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FFB00D18"/>
@@ -3042,7 +3410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FFB00D18"/>
@@ -3765,7 +4133,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FFB00D18"/>
@@ -4547,7 +4915,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A8132A"/>

--- a/assets/files/coca-cola-business-model.xlsx
+++ b/assets/files/coca-cola-business-model.xlsx
@@ -1376,7 +1376,7 @@
     <row r="2">
       <c r="A2" s="58" t="inlineStr">
         <is>
-          <t>USD; per-share USD. Dividend aristocrat (63+ yrs) — DDM-led. Live $82 (Jul 2026), 4,310M shares, net debt ~$29bn.</t>
+          <t>USD; per-share USD. Dividend King (64 yrs) — DDM-led valuation. Live $87 (28-Jul-2026), post-Q2 record high.</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B5" s="141" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="B9" s="58" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="10">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B11" s="141" t="n">
-        <v>15100</v>
+        <v>15300</v>
       </c>
     </row>
     <row r="12">
@@ -1633,7 +1633,7 @@
     <row r="25">
       <c r="A25" s="58" t="inlineStr">
         <is>
-          <t>Upside / (downside) vs $82</t>
+          <t>Upside / (downside) vs price</t>
         </is>
       </c>
       <c r="B25" s="144">
@@ -4951,10 +4951,8 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="B4" s="124" t="inlineStr">
-        <is>
-          <t>Price ($)</t>
-        </is>
+      <c r="B4" s="124" t="n">
+        <v>87</v>
       </c>
       <c r="C4" s="124" t="inlineStr">
         <is>
